--- a/FastPai/data_mode.xlsx
+++ b/FastPai/data_mode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29405"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\pythonProject3\FastPai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B32F6FE-3101-4ECC-BCDE-FFAE2C6822D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7FC0B0-1002-4F0E-BEB1-B4300FBADD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1295" yWindow="3219" windowWidth="17425" windowHeight="9051" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>num_tasks</t>
   </si>
@@ -371,16 +371,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -416,189 +408,9 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -609,7 +421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05B81C0-BEE4-4BAD-8E37-26A00BF28D8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A090D1-A506-4B51-BFEA-0DBEA190AB90}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/FastPai/data_mode.xlsx
+++ b/FastPai/data_mode.xlsx
@@ -447,10 +447,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K349"/>
+  <dimension ref="A1:K398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.95"/>
   <sheetData>
     <row r="1">
@@ -14083,6 +14083,1917 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:49:46</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>5</v>
+      </c>
+      <c r="C350" t="n">
+        <v>15</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1</v>
+      </c>
+      <c r="E350" t="n">
+        <v>3</v>
+      </c>
+      <c r="F350" t="n">
+        <v>4</v>
+      </c>
+      <c r="G350" t="n">
+        <v>269</v>
+      </c>
+      <c r="H350" t="n">
+        <v>520</v>
+      </c>
+      <c r="I350" t="n">
+        <v>4</v>
+      </c>
+      <c r="J350" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [1, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:49:46</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>5</v>
+      </c>
+      <c r="C351" t="n">
+        <v>15</v>
+      </c>
+      <c r="D351" t="n">
+        <v>1</v>
+      </c>
+      <c r="E351" t="n">
+        <v>3</v>
+      </c>
+      <c r="F351" t="n">
+        <v>4</v>
+      </c>
+      <c r="G351" t="n">
+        <v>226</v>
+      </c>
+      <c r="H351" t="n">
+        <v>468</v>
+      </c>
+      <c r="I351" t="n">
+        <v>4</v>
+      </c>
+      <c r="J351" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 1, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:49:46</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>5</v>
+      </c>
+      <c r="C352" t="n">
+        <v>15</v>
+      </c>
+      <c r="D352" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" t="n">
+        <v>3</v>
+      </c>
+      <c r="F352" t="n">
+        <v>4</v>
+      </c>
+      <c r="G352" t="n">
+        <v>247</v>
+      </c>
+      <c r="H352" t="n">
+        <v>480</v>
+      </c>
+      <c r="I352" t="n">
+        <v>4</v>
+      </c>
+      <c r="J352" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [1, 0, 1, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:49:46</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>5</v>
+      </c>
+      <c r="C353" t="n">
+        <v>15</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1</v>
+      </c>
+      <c r="E353" t="n">
+        <v>3</v>
+      </c>
+      <c r="F353" t="n">
+        <v>4</v>
+      </c>
+      <c r="G353" t="n">
+        <v>203</v>
+      </c>
+      <c r="H353" t="n">
+        <v>438</v>
+      </c>
+      <c r="I353" t="n">
+        <v>4</v>
+      </c>
+      <c r="J353" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:54:24</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>5</v>
+      </c>
+      <c r="C354" t="n">
+        <v>15</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" t="n">
+        <v>3</v>
+      </c>
+      <c r="F354" t="n">
+        <v>4</v>
+      </c>
+      <c r="G354" t="n">
+        <v>255</v>
+      </c>
+      <c r="H354" t="n">
+        <v>438</v>
+      </c>
+      <c r="I354" t="n">
+        <v>4</v>
+      </c>
+      <c r="J354" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [1, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:54:24</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>5</v>
+      </c>
+      <c r="C355" t="n">
+        <v>15</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" t="n">
+        <v>3</v>
+      </c>
+      <c r="F355" t="n">
+        <v>4</v>
+      </c>
+      <c r="G355" t="n">
+        <v>240</v>
+      </c>
+      <c r="H355" t="n">
+        <v>335</v>
+      </c>
+      <c r="I355" t="n">
+        <v>4</v>
+      </c>
+      <c r="J355" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0], [1, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:54:24</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>5</v>
+      </c>
+      <c r="C356" t="n">
+        <v>15</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="n">
+        <v>3</v>
+      </c>
+      <c r="F356" t="n">
+        <v>4</v>
+      </c>
+      <c r="G356" t="n">
+        <v>244</v>
+      </c>
+      <c r="H356" t="n">
+        <v>410</v>
+      </c>
+      <c r="I356" t="n">
+        <v>4</v>
+      </c>
+      <c r="J356" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 1, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:54:24</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>5</v>
+      </c>
+      <c r="C357" t="n">
+        <v>15</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" t="n">
+        <v>3</v>
+      </c>
+      <c r="F357" t="n">
+        <v>4</v>
+      </c>
+      <c r="G357" t="n">
+        <v>295</v>
+      </c>
+      <c r="H357" t="n">
+        <v>456</v>
+      </c>
+      <c r="I357" t="n">
+        <v>4</v>
+      </c>
+      <c r="J357" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 1, 0, 1, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:59:35</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>5</v>
+      </c>
+      <c r="C358" t="n">
+        <v>15</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1</v>
+      </c>
+      <c r="E358" t="n">
+        <v>3</v>
+      </c>
+      <c r="F358" t="n">
+        <v>4</v>
+      </c>
+      <c r="G358" t="n">
+        <v>230</v>
+      </c>
+      <c r="H358" t="n">
+        <v>494</v>
+      </c>
+      <c r="I358" t="n">
+        <v>2</v>
+      </c>
+      <c r="J358" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>[[1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-10-08 16:59:35</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>5</v>
+      </c>
+      <c r="C359" t="n">
+        <v>15</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" t="n">
+        <v>3</v>
+      </c>
+      <c r="F359" t="n">
+        <v>4</v>
+      </c>
+      <c r="G359" t="n">
+        <v>231</v>
+      </c>
+      <c r="H359" t="n">
+        <v>506</v>
+      </c>
+      <c r="I359" t="n">
+        <v>2</v>
+      </c>
+      <c r="J359" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>[[1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:04:15</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>5</v>
+      </c>
+      <c r="C360" t="n">
+        <v>15</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="n">
+        <v>3</v>
+      </c>
+      <c r="F360" t="n">
+        <v>4</v>
+      </c>
+      <c r="G360" t="n">
+        <v>306</v>
+      </c>
+      <c r="H360" t="n">
+        <v>498</v>
+      </c>
+      <c r="I360" t="n">
+        <v>4</v>
+      </c>
+      <c r="J360" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:04:15</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>5</v>
+      </c>
+      <c r="C361" t="n">
+        <v>15</v>
+      </c>
+      <c r="D361" t="n">
+        <v>1</v>
+      </c>
+      <c r="E361" t="n">
+        <v>3</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4</v>
+      </c>
+      <c r="G361" t="n">
+        <v>271</v>
+      </c>
+      <c r="H361" t="n">
+        <v>414</v>
+      </c>
+      <c r="I361" t="n">
+        <v>4</v>
+      </c>
+      <c r="J361" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 1, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:04:15</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>5</v>
+      </c>
+      <c r="C362" t="n">
+        <v>15</v>
+      </c>
+      <c r="D362" t="n">
+        <v>1</v>
+      </c>
+      <c r="E362" t="n">
+        <v>3</v>
+      </c>
+      <c r="F362" t="n">
+        <v>4</v>
+      </c>
+      <c r="G362" t="n">
+        <v>312</v>
+      </c>
+      <c r="H362" t="n">
+        <v>514</v>
+      </c>
+      <c r="I362" t="n">
+        <v>4</v>
+      </c>
+      <c r="J362" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:04:15</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>5</v>
+      </c>
+      <c r="C363" t="n">
+        <v>15</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" t="n">
+        <v>3</v>
+      </c>
+      <c r="F363" t="n">
+        <v>4</v>
+      </c>
+      <c r="G363" t="n">
+        <v>281</v>
+      </c>
+      <c r="H363" t="n">
+        <v>463</v>
+      </c>
+      <c r="I363" t="n">
+        <v>4</v>
+      </c>
+      <c r="J363" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 1, 0, 1, 1, 0, 0, 0, 0, 1, 0, 0, 1, 1, 0], [1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:08:06</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>5</v>
+      </c>
+      <c r="C364" t="n">
+        <v>15</v>
+      </c>
+      <c r="D364" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" t="n">
+        <v>3</v>
+      </c>
+      <c r="F364" t="n">
+        <v>4</v>
+      </c>
+      <c r="G364" t="n">
+        <v>278</v>
+      </c>
+      <c r="H364" t="n">
+        <v>513</v>
+      </c>
+      <c r="I364" t="n">
+        <v>3</v>
+      </c>
+      <c r="J364" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 1, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:08:06</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>5</v>
+      </c>
+      <c r="C365" t="n">
+        <v>15</v>
+      </c>
+      <c r="D365" t="n">
+        <v>1</v>
+      </c>
+      <c r="E365" t="n">
+        <v>3</v>
+      </c>
+      <c r="F365" t="n">
+        <v>4</v>
+      </c>
+      <c r="G365" t="n">
+        <v>274</v>
+      </c>
+      <c r="H365" t="n">
+        <v>449</v>
+      </c>
+      <c r="I365" t="n">
+        <v>3</v>
+      </c>
+      <c r="J365" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0, 0, 1, 1, 0], [1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 1, 1, 0, 0, 1, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:08:06</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>5</v>
+      </c>
+      <c r="C366" t="n">
+        <v>15</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1</v>
+      </c>
+      <c r="E366" t="n">
+        <v>3</v>
+      </c>
+      <c r="F366" t="n">
+        <v>4</v>
+      </c>
+      <c r="G366" t="n">
+        <v>268</v>
+      </c>
+      <c r="H366" t="n">
+        <v>438</v>
+      </c>
+      <c r="I366" t="n">
+        <v>3</v>
+      </c>
+      <c r="J366" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 1, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:12:42</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>5</v>
+      </c>
+      <c r="C367" t="n">
+        <v>15</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" t="n">
+        <v>3</v>
+      </c>
+      <c r="F367" t="n">
+        <v>4</v>
+      </c>
+      <c r="G367" t="n">
+        <v>247</v>
+      </c>
+      <c r="H367" t="n">
+        <v>512</v>
+      </c>
+      <c r="I367" t="n">
+        <v>2</v>
+      </c>
+      <c r="J367" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [1, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [0, 1, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:12:42</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>5</v>
+      </c>
+      <c r="C368" t="n">
+        <v>15</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1</v>
+      </c>
+      <c r="E368" t="n">
+        <v>3</v>
+      </c>
+      <c r="F368" t="n">
+        <v>4</v>
+      </c>
+      <c r="G368" t="n">
+        <v>232</v>
+      </c>
+      <c r="H368" t="n">
+        <v>485</v>
+      </c>
+      <c r="I368" t="n">
+        <v>2</v>
+      </c>
+      <c r="J368" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [1, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:19:36</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>5</v>
+      </c>
+      <c r="C369" t="n">
+        <v>15</v>
+      </c>
+      <c r="D369" t="n">
+        <v>1</v>
+      </c>
+      <c r="E369" t="n">
+        <v>3</v>
+      </c>
+      <c r="F369" t="n">
+        <v>4</v>
+      </c>
+      <c r="G369" t="n">
+        <v>215</v>
+      </c>
+      <c r="H369" t="n">
+        <v>368</v>
+      </c>
+      <c r="I369" t="n">
+        <v>4</v>
+      </c>
+      <c r="J369" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 1, 1, 0], [0, 0, 1, 1, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:19:36</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>5</v>
+      </c>
+      <c r="C370" t="n">
+        <v>15</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1</v>
+      </c>
+      <c r="E370" t="n">
+        <v>3</v>
+      </c>
+      <c r="F370" t="n">
+        <v>4</v>
+      </c>
+      <c r="G370" t="n">
+        <v>202</v>
+      </c>
+      <c r="H370" t="n">
+        <v>360</v>
+      </c>
+      <c r="I370" t="n">
+        <v>4</v>
+      </c>
+      <c r="J370" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:19:36</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>5</v>
+      </c>
+      <c r="C371" t="n">
+        <v>15</v>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+      <c r="E371" t="n">
+        <v>3</v>
+      </c>
+      <c r="F371" t="n">
+        <v>4</v>
+      </c>
+      <c r="G371" t="n">
+        <v>246</v>
+      </c>
+      <c r="H371" t="n">
+        <v>436</v>
+      </c>
+      <c r="I371" t="n">
+        <v>4</v>
+      </c>
+      <c r="J371" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:19:36</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>5</v>
+      </c>
+      <c r="C372" t="n">
+        <v>15</v>
+      </c>
+      <c r="D372" t="n">
+        <v>1</v>
+      </c>
+      <c r="E372" t="n">
+        <v>3</v>
+      </c>
+      <c r="F372" t="n">
+        <v>4</v>
+      </c>
+      <c r="G372" t="n">
+        <v>252</v>
+      </c>
+      <c r="H372" t="n">
+        <v>456</v>
+      </c>
+      <c r="I372" t="n">
+        <v>4</v>
+      </c>
+      <c r="J372" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1], [0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:23:42</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>5</v>
+      </c>
+      <c r="C373" t="n">
+        <v>15</v>
+      </c>
+      <c r="D373" t="n">
+        <v>1</v>
+      </c>
+      <c r="E373" t="n">
+        <v>3</v>
+      </c>
+      <c r="F373" t="n">
+        <v>4</v>
+      </c>
+      <c r="G373" t="n">
+        <v>255</v>
+      </c>
+      <c r="H373" t="n">
+        <v>480</v>
+      </c>
+      <c r="I373" t="n">
+        <v>3</v>
+      </c>
+      <c r="J373" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:23:42</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>5</v>
+      </c>
+      <c r="C374" t="n">
+        <v>15</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" t="n">
+        <v>3</v>
+      </c>
+      <c r="F374" t="n">
+        <v>4</v>
+      </c>
+      <c r="G374" t="n">
+        <v>253</v>
+      </c>
+      <c r="H374" t="n">
+        <v>472</v>
+      </c>
+      <c r="I374" t="n">
+        <v>3</v>
+      </c>
+      <c r="J374" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:23:42</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>5</v>
+      </c>
+      <c r="C375" t="n">
+        <v>15</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" t="n">
+        <v>3</v>
+      </c>
+      <c r="F375" t="n">
+        <v>4</v>
+      </c>
+      <c r="G375" t="n">
+        <v>270</v>
+      </c>
+      <c r="H375" t="n">
+        <v>516</v>
+      </c>
+      <c r="I375" t="n">
+        <v>3</v>
+      </c>
+      <c r="J375" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>[[1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:28:18</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>5</v>
+      </c>
+      <c r="C376" t="n">
+        <v>15</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1</v>
+      </c>
+      <c r="E376" t="n">
+        <v>3</v>
+      </c>
+      <c r="F376" t="n">
+        <v>4</v>
+      </c>
+      <c r="G376" t="n">
+        <v>274</v>
+      </c>
+      <c r="H376" t="n">
+        <v>515</v>
+      </c>
+      <c r="I376" t="n">
+        <v>4</v>
+      </c>
+      <c r="J376" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 1, 0], [0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:28:18</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>5</v>
+      </c>
+      <c r="C377" t="n">
+        <v>15</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1</v>
+      </c>
+      <c r="E377" t="n">
+        <v>3</v>
+      </c>
+      <c r="F377" t="n">
+        <v>4</v>
+      </c>
+      <c r="G377" t="n">
+        <v>252</v>
+      </c>
+      <c r="H377" t="n">
+        <v>478</v>
+      </c>
+      <c r="I377" t="n">
+        <v>4</v>
+      </c>
+      <c r="J377" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>[[1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:28:18</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>5</v>
+      </c>
+      <c r="C378" t="n">
+        <v>15</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
+      <c r="E378" t="n">
+        <v>3</v>
+      </c>
+      <c r="F378" t="n">
+        <v>4</v>
+      </c>
+      <c r="G378" t="n">
+        <v>264</v>
+      </c>
+      <c r="H378" t="n">
+        <v>488</v>
+      </c>
+      <c r="I378" t="n">
+        <v>4</v>
+      </c>
+      <c r="J378" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:28:18</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>5</v>
+      </c>
+      <c r="C379" t="n">
+        <v>15</v>
+      </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
+      <c r="E379" t="n">
+        <v>3</v>
+      </c>
+      <c r="F379" t="n">
+        <v>4</v>
+      </c>
+      <c r="G379" t="n">
+        <v>243</v>
+      </c>
+      <c r="H379" t="n">
+        <v>443</v>
+      </c>
+      <c r="I379" t="n">
+        <v>4</v>
+      </c>
+      <c r="J379" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 1, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:32:55</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>5</v>
+      </c>
+      <c r="C380" t="n">
+        <v>15</v>
+      </c>
+      <c r="D380" t="n">
+        <v>1</v>
+      </c>
+      <c r="E380" t="n">
+        <v>3</v>
+      </c>
+      <c r="F380" t="n">
+        <v>4</v>
+      </c>
+      <c r="G380" t="n">
+        <v>260</v>
+      </c>
+      <c r="H380" t="n">
+        <v>489</v>
+      </c>
+      <c r="I380" t="n">
+        <v>3</v>
+      </c>
+      <c r="J380" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0], [0, 1, 1, 0, 0, 1, 0, 0, 0, 1, 0, 1, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:32:55</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>5</v>
+      </c>
+      <c r="C381" t="n">
+        <v>15</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1</v>
+      </c>
+      <c r="E381" t="n">
+        <v>3</v>
+      </c>
+      <c r="F381" t="n">
+        <v>4</v>
+      </c>
+      <c r="G381" t="n">
+        <v>267</v>
+      </c>
+      <c r="H381" t="n">
+        <v>502</v>
+      </c>
+      <c r="I381" t="n">
+        <v>3</v>
+      </c>
+      <c r="J381" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [1, 1, 0, 1, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:32:55</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>5</v>
+      </c>
+      <c r="C382" t="n">
+        <v>15</v>
+      </c>
+      <c r="D382" t="n">
+        <v>1</v>
+      </c>
+      <c r="E382" t="n">
+        <v>3</v>
+      </c>
+      <c r="F382" t="n">
+        <v>4</v>
+      </c>
+      <c r="G382" t="n">
+        <v>234</v>
+      </c>
+      <c r="H382" t="n">
+        <v>382</v>
+      </c>
+      <c r="I382" t="n">
+        <v>3</v>
+      </c>
+      <c r="J382" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 0, 0], [1, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:36:49</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>5</v>
+      </c>
+      <c r="C383" t="n">
+        <v>15</v>
+      </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383" t="n">
+        <v>3</v>
+      </c>
+      <c r="F383" t="n">
+        <v>4</v>
+      </c>
+      <c r="G383" t="n">
+        <v>254</v>
+      </c>
+      <c r="H383" t="n">
+        <v>537</v>
+      </c>
+      <c r="I383" t="n">
+        <v>3</v>
+      </c>
+      <c r="J383" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:36:49</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>5</v>
+      </c>
+      <c r="C384" t="n">
+        <v>15</v>
+      </c>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" t="n">
+        <v>3</v>
+      </c>
+      <c r="F384" t="n">
+        <v>4</v>
+      </c>
+      <c r="G384" t="n">
+        <v>268</v>
+      </c>
+      <c r="H384" t="n">
+        <v>538</v>
+      </c>
+      <c r="I384" t="n">
+        <v>3</v>
+      </c>
+      <c r="J384" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 1, 0, 1, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:36:49</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>5</v>
+      </c>
+      <c r="C385" t="n">
+        <v>15</v>
+      </c>
+      <c r="D385" t="n">
+        <v>1</v>
+      </c>
+      <c r="E385" t="n">
+        <v>3</v>
+      </c>
+      <c r="F385" t="n">
+        <v>4</v>
+      </c>
+      <c r="G385" t="n">
+        <v>240</v>
+      </c>
+      <c r="H385" t="n">
+        <v>534</v>
+      </c>
+      <c r="I385" t="n">
+        <v>3</v>
+      </c>
+      <c r="J385" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:40:37</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>5</v>
+      </c>
+      <c r="C386" t="n">
+        <v>15</v>
+      </c>
+      <c r="D386" t="n">
+        <v>1</v>
+      </c>
+      <c r="E386" t="n">
+        <v>3</v>
+      </c>
+      <c r="F386" t="n">
+        <v>4</v>
+      </c>
+      <c r="G386" t="n">
+        <v>278</v>
+      </c>
+      <c r="H386" t="n">
+        <v>465</v>
+      </c>
+      <c r="I386" t="n">
+        <v>3</v>
+      </c>
+      <c r="J386" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 0], [1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:40:37</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>5</v>
+      </c>
+      <c r="C387" t="n">
+        <v>15</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" t="n">
+        <v>3</v>
+      </c>
+      <c r="F387" t="n">
+        <v>4</v>
+      </c>
+      <c r="G387" t="n">
+        <v>278</v>
+      </c>
+      <c r="H387" t="n">
+        <v>512</v>
+      </c>
+      <c r="I387" t="n">
+        <v>3</v>
+      </c>
+      <c r="J387" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>[[1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:40:37</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>5</v>
+      </c>
+      <c r="C388" t="n">
+        <v>15</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" t="n">
+        <v>3</v>
+      </c>
+      <c r="F388" t="n">
+        <v>4</v>
+      </c>
+      <c r="G388" t="n">
+        <v>267</v>
+      </c>
+      <c r="H388" t="n">
+        <v>356</v>
+      </c>
+      <c r="I388" t="n">
+        <v>3</v>
+      </c>
+      <c r="J388" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:44:52</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>5</v>
+      </c>
+      <c r="C389" t="n">
+        <v>15</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1</v>
+      </c>
+      <c r="E389" t="n">
+        <v>3</v>
+      </c>
+      <c r="F389" t="n">
+        <v>4</v>
+      </c>
+      <c r="G389" t="n">
+        <v>250</v>
+      </c>
+      <c r="H389" t="n">
+        <v>418</v>
+      </c>
+      <c r="I389" t="n">
+        <v>3</v>
+      </c>
+      <c r="J389" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:44:52</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>5</v>
+      </c>
+      <c r="C390" t="n">
+        <v>15</v>
+      </c>
+      <c r="D390" t="n">
+        <v>1</v>
+      </c>
+      <c r="E390" t="n">
+        <v>3</v>
+      </c>
+      <c r="F390" t="n">
+        <v>4</v>
+      </c>
+      <c r="G390" t="n">
+        <v>242</v>
+      </c>
+      <c r="H390" t="n">
+        <v>406</v>
+      </c>
+      <c r="I390" t="n">
+        <v>3</v>
+      </c>
+      <c r="J390" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [1, 0, 1, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:44:52</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>5</v>
+      </c>
+      <c r="C391" t="n">
+        <v>15</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1</v>
+      </c>
+      <c r="E391" t="n">
+        <v>3</v>
+      </c>
+      <c r="F391" t="n">
+        <v>4</v>
+      </c>
+      <c r="G391" t="n">
+        <v>262</v>
+      </c>
+      <c r="H391" t="n">
+        <v>510</v>
+      </c>
+      <c r="I391" t="n">
+        <v>3</v>
+      </c>
+      <c r="J391" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:49:24</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>5</v>
+      </c>
+      <c r="C392" t="n">
+        <v>15</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1</v>
+      </c>
+      <c r="E392" t="n">
+        <v>3</v>
+      </c>
+      <c r="F392" t="n">
+        <v>4</v>
+      </c>
+      <c r="G392" t="n">
+        <v>286</v>
+      </c>
+      <c r="H392" t="n">
+        <v>516</v>
+      </c>
+      <c r="I392" t="n">
+        <v>4</v>
+      </c>
+      <c r="J392" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0], [1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:49:24</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>5</v>
+      </c>
+      <c r="C393" t="n">
+        <v>15</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393" t="n">
+        <v>3</v>
+      </c>
+      <c r="F393" t="n">
+        <v>4</v>
+      </c>
+      <c r="G393" t="n">
+        <v>241</v>
+      </c>
+      <c r="H393" t="n">
+        <v>499</v>
+      </c>
+      <c r="I393" t="n">
+        <v>4</v>
+      </c>
+      <c r="J393" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 1, 0], [1, 1, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:49:24</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>5</v>
+      </c>
+      <c r="C394" t="n">
+        <v>15</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1</v>
+      </c>
+      <c r="E394" t="n">
+        <v>3</v>
+      </c>
+      <c r="F394" t="n">
+        <v>4</v>
+      </c>
+      <c r="G394" t="n">
+        <v>278</v>
+      </c>
+      <c r="H394" t="n">
+        <v>500</v>
+      </c>
+      <c r="I394" t="n">
+        <v>4</v>
+      </c>
+      <c r="J394" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [1, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0], [0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:49:24</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>5</v>
+      </c>
+      <c r="C395" t="n">
+        <v>15</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" t="n">
+        <v>3</v>
+      </c>
+      <c r="F395" t="n">
+        <v>4</v>
+      </c>
+      <c r="G395" t="n">
+        <v>216</v>
+      </c>
+      <c r="H395" t="n">
+        <v>465</v>
+      </c>
+      <c r="I395" t="n">
+        <v>4</v>
+      </c>
+      <c r="J395" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>[[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0], [0, 1, 0, 1, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0], [0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0], [0, 0, 1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0], [1, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:53:15</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>5</v>
+      </c>
+      <c r="C396" t="n">
+        <v>15</v>
+      </c>
+      <c r="D396" t="n">
+        <v>1</v>
+      </c>
+      <c r="E396" t="n">
+        <v>3</v>
+      </c>
+      <c r="F396" t="n">
+        <v>4</v>
+      </c>
+      <c r="G396" t="n">
+        <v>259</v>
+      </c>
+      <c r="H396" t="n">
+        <v>539</v>
+      </c>
+      <c r="I396" t="n">
+        <v>3</v>
+      </c>
+      <c r="J396" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:53:15</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>5</v>
+      </c>
+      <c r="C397" t="n">
+        <v>15</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1</v>
+      </c>
+      <c r="E397" t="n">
+        <v>3</v>
+      </c>
+      <c r="F397" t="n">
+        <v>4</v>
+      </c>
+      <c r="G397" t="n">
+        <v>232</v>
+      </c>
+      <c r="H397" t="n">
+        <v>439</v>
+      </c>
+      <c r="I397" t="n">
+        <v>3</v>
+      </c>
+      <c r="J397" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>[[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1], [0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0], [0, 0, 0, 1, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025-10-08 17:53:15</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>5</v>
+      </c>
+      <c r="C398" t="n">
+        <v>15</v>
+      </c>
+      <c r="D398" t="n">
+        <v>1</v>
+      </c>
+      <c r="E398" t="n">
+        <v>3</v>
+      </c>
+      <c r="F398" t="n">
+        <v>4</v>
+      </c>
+      <c r="G398" t="n">
+        <v>240</v>
+      </c>
+      <c r="H398" t="n">
+        <v>469</v>
+      </c>
+      <c r="I398" t="n">
+        <v>3</v>
+      </c>
+      <c r="J398" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>[[0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1], [0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0], [0, 0, 0, 1, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0], [0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0], [0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
